--- a/ModuCard-Backplane-Sixth-Sense/Documents/ModuCardPinoutCreator.xlsx
+++ b/ModuCard-Backplane-Sixth-Sense/Documents/ModuCardPinoutCreator.xlsx
@@ -22,25 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="73">
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ModuCard Pinout </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Creator</t>
-    </r>
+    <t xml:space="preserve">ModuCard Pinout Creator</t>
   </si>
   <si>
     <t xml:space="preserve">ROW A</t>
@@ -267,7 +249,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,12 +271,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -661,16 +637,16 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -691,7 +667,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -711,7 +687,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -719,11 +695,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -743,7 +719,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -751,7 +727,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -771,15 +747,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="2" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="3" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="3" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -795,11 +771,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="27" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -819,11 +795,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="21" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="21" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -835,15 +811,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -851,11 +827,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -867,19 +843,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -895,7 +871,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -903,7 +879,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="22" borderId="2" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -911,11 +887,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="21" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="21" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1180,7 +1156,7 @@
   <dimension ref="A1:AG20"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.74"/>
